--- a/Results/Tests2.xlsx
+++ b/Results/Tests2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irma1\Documents\Tesis_tests\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8BFA21-4103-49D6-BE05-645C1C5EA7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095DFA23-203D-4B73-ABBE-B9D29866636F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="10980" windowHeight="13770" xr2:uid="{9811F352-0CC2-49A3-8C55-61560FCE2FC5}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="21820" windowHeight="13900" xr2:uid="{9811F352-0CC2-49A3-8C55-61560FCE2FC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Prueba</t>
   </si>
@@ -188,52 +188,13 @@
     <t>MT45</t>
   </si>
   <si>
-    <t>MT46</t>
-  </si>
-  <si>
-    <t>MT47</t>
-  </si>
-  <si>
-    <t>MT48</t>
-  </si>
-  <si>
-    <t>MT49</t>
-  </si>
-  <si>
-    <t>MT50</t>
-  </si>
-  <si>
-    <t>MT51</t>
-  </si>
-  <si>
-    <t>MT52</t>
-  </si>
-  <si>
-    <t>MT53</t>
-  </si>
-  <si>
-    <t>MT54</t>
-  </si>
-  <si>
-    <t>MT55</t>
-  </si>
-  <si>
-    <t>MT56</t>
-  </si>
-  <si>
-    <t>MT57</t>
-  </si>
-  <si>
-    <t>MT58</t>
-  </si>
-  <si>
-    <t>MT59</t>
-  </si>
-  <si>
-    <t>MT60</t>
-  </si>
-  <si>
     <t>Payload (Bytes)</t>
+  </si>
+  <si>
+    <t>Mosquitto</t>
+  </si>
+  <si>
+    <t>Rust</t>
   </si>
 </sst>
 </file>
@@ -255,12 +216,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -275,9 +242,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842D6BDC-3AC3-4C20-B433-D06981D498A1}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
@@ -620,7 +588,7 @@
     <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +599,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -639,8 +607,14 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -659,8 +633,9 @@
       <c r="F2">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -679,8 +654,9 @@
       <c r="F3">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -699,8 +675,9 @@
       <c r="F4">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -719,8 +696,9 @@
       <c r="F5">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -739,8 +717,9 @@
       <c r="F6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -759,8 +738,9 @@
       <c r="F7">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -779,8 +759,9 @@
       <c r="F8">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -799,8 +780,9 @@
       <c r="F9">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -819,8 +801,9 @@
       <c r="F10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -839,8 +822,9 @@
       <c r="F11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -859,8 +843,9 @@
       <c r="F12">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -879,8 +864,9 @@
       <c r="F13">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -899,8 +885,9 @@
       <c r="F14">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -919,8 +906,9 @@
       <c r="F15">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -939,16 +927,17 @@
       <c r="F16">
         <v>1</v>
       </c>
+      <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -965,10 +954,10 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>100</v>
@@ -985,10 +974,10 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -1005,10 +994,10 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -1025,10 +1014,10 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -1045,10 +1034,10 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1">
         <v>1000</v>
@@ -1065,10 +1054,10 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1">
         <v>1000</v>
@@ -1085,10 +1074,10 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D24" s="1">
         <v>1000</v>
@@ -1105,10 +1094,10 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C25">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1">
         <v>1000</v>
@@ -1125,10 +1114,10 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D26" s="1">
         <v>1000</v>
@@ -1145,10 +1134,10 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1">
         <v>10000</v>
@@ -1165,10 +1154,10 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C28">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D28" s="1">
         <v>10000</v>
@@ -1185,10 +1174,10 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D29" s="1">
         <v>10000</v>
@@ -1205,10 +1194,10 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D30" s="1">
         <v>10000</v>
@@ -1225,10 +1214,10 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1">
         <v>10000</v>
@@ -1245,10 +1234,10 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C32">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -1265,10 +1254,10 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C33">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -1285,10 +1274,10 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C34">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -1305,10 +1294,10 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C35">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -1325,10 +1314,10 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C36">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -1345,10 +1334,10 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C37">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D37" s="1">
         <v>1000</v>
@@ -1365,10 +1354,10 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C38">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D38" s="1">
         <v>1000</v>
@@ -1385,10 +1374,10 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C39">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D39" s="1">
         <v>1000</v>
@@ -1405,10 +1394,10 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C40">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D40" s="1">
         <v>1000</v>
@@ -1425,10 +1414,10 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C41">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D41" s="1">
         <v>1000</v>
@@ -1445,10 +1434,10 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C42">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D42" s="1">
         <v>10000</v>
@@ -1465,10 +1454,10 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C43">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D43" s="1">
         <v>10000</v>
@@ -1485,10 +1474,10 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C44">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D44" s="1">
         <v>10000</v>
@@ -1505,10 +1494,10 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C45">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D45" s="1">
         <v>10000</v>
@@ -1525,10 +1514,10 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C46">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D46" s="1">
         <v>10000</v>
@@ -1537,306 +1526,6 @@
         <v>120</v>
       </c>
       <c r="F46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47">
-        <v>50</v>
-      </c>
-      <c r="C47">
-        <v>50</v>
-      </c>
-      <c r="D47">
-        <v>100</v>
-      </c>
-      <c r="E47">
-        <v>120</v>
-      </c>
-      <c r="F47">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48">
-        <v>50</v>
-      </c>
-      <c r="C48">
-        <v>50</v>
-      </c>
-      <c r="D48">
-        <v>100</v>
-      </c>
-      <c r="E48">
-        <v>120</v>
-      </c>
-      <c r="F48">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49">
-        <v>50</v>
-      </c>
-      <c r="C49">
-        <v>50</v>
-      </c>
-      <c r="D49">
-        <v>100</v>
-      </c>
-      <c r="E49">
-        <v>120</v>
-      </c>
-      <c r="F49">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50">
-        <v>50</v>
-      </c>
-      <c r="C50">
-        <v>50</v>
-      </c>
-      <c r="D50">
-        <v>100</v>
-      </c>
-      <c r="E50">
-        <v>120</v>
-      </c>
-      <c r="F50">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51">
-        <v>50</v>
-      </c>
-      <c r="C51">
-        <v>50</v>
-      </c>
-      <c r="D51">
-        <v>100</v>
-      </c>
-      <c r="E51">
-        <v>120</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52">
-        <v>50</v>
-      </c>
-      <c r="C52">
-        <v>50</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E52">
-        <v>120</v>
-      </c>
-      <c r="F52">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53">
-        <v>50</v>
-      </c>
-      <c r="C53">
-        <v>50</v>
-      </c>
-      <c r="D53" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E53">
-        <v>120</v>
-      </c>
-      <c r="F53">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54">
-        <v>50</v>
-      </c>
-      <c r="C54">
-        <v>50</v>
-      </c>
-      <c r="D54" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E54">
-        <v>120</v>
-      </c>
-      <c r="F54">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55">
-        <v>50</v>
-      </c>
-      <c r="C55">
-        <v>50</v>
-      </c>
-      <c r="D55" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E55">
-        <v>120</v>
-      </c>
-      <c r="F55">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>59</v>
-      </c>
-      <c r="B56">
-        <v>50</v>
-      </c>
-      <c r="C56">
-        <v>50</v>
-      </c>
-      <c r="D56" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E56">
-        <v>120</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57">
-        <v>50</v>
-      </c>
-      <c r="C57">
-        <v>50</v>
-      </c>
-      <c r="D57" s="1">
-        <v>10000</v>
-      </c>
-      <c r="E57">
-        <v>120</v>
-      </c>
-      <c r="F57">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58">
-        <v>50</v>
-      </c>
-      <c r="C58">
-        <v>50</v>
-      </c>
-      <c r="D58" s="1">
-        <v>10000</v>
-      </c>
-      <c r="E58">
-        <v>120</v>
-      </c>
-      <c r="F58">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59">
-        <v>50</v>
-      </c>
-      <c r="C59">
-        <v>50</v>
-      </c>
-      <c r="D59" s="1">
-        <v>10000</v>
-      </c>
-      <c r="E59">
-        <v>120</v>
-      </c>
-      <c r="F59">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60">
-        <v>50</v>
-      </c>
-      <c r="C60">
-        <v>50</v>
-      </c>
-      <c r="D60" s="1">
-        <v>10000</v>
-      </c>
-      <c r="E60">
-        <v>120</v>
-      </c>
-      <c r="F60">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B61">
-        <v>50</v>
-      </c>
-      <c r="C61">
-        <v>50</v>
-      </c>
-      <c r="D61" s="1">
-        <v>10000</v>
-      </c>
-      <c r="E61">
-        <v>120</v>
-      </c>
-      <c r="F61">
         <v>1</v>
       </c>
     </row>
